--- a/artfynd/A 26240-2019 artfynd.xlsx
+++ b/artfynd/A 26240-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 26240-2019 artfynd.xlsx
+++ b/artfynd/A 26240-2019 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>86715765</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552347.8179873455</v>
+        <v>552348</v>
       </c>
       <c r="R7" t="n">
-        <v>6910756.87694683</v>
+        <v>6910757</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1312,19 +1312,9 @@
           <t>2020-07-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-07-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 26240-2019 artfynd.xlsx
+++ b/artfynd/A 26240-2019 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>86715765</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 26240-2019 artfynd.xlsx
+++ b/artfynd/A 26240-2019 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>86715765</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
